--- a/output/pdf_financials_xlsx/BATX.xlsx
+++ b/output/pdf_financials_xlsx/BATX.xlsx
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.59545</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.319888</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.494129</v>
       </c>
     </row>
     <row r="93">
@@ -2359,7 +2359,7 @@
         <v>-0.05076</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.08222400000000001</v>
       </c>
     </row>
     <row r="119">
@@ -2810,7 +2810,11 @@
           <t>Prepaids and deposits 6,12</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -3159,7 +3163,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3661,7 +3669,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>1.59545</v>
       </c>
@@ -4471,7 +4483,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BATX.xlsx
+++ b/output/pdf_financials_xlsx/BATX.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.051577</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.6088249999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.037874</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.051577</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.6088249999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.037874</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.070034</v>
+        <v>0.018457</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.923583</v>
+        <v>0.314758</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.29495</v>
+        <v>0.257076</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">

--- a/output/pdf_financials_xlsx/BATX.xlsx
+++ b/output/pdf_financials_xlsx/BATX.xlsx
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.869388</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.797437</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.407609</v>
       </c>
     </row>
     <row r="65">
@@ -1528,7 +1528,7 @@
         <v>1.074548</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.448155</v>
       </c>
     </row>
     <row r="68">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>1.455364</v>
+        <v>2.324752</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>1.074548</v>
@@ -3861,7 +3861,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>-0.00481</v>
       </c>
